--- a/Result/checksun_type/工業自動化.xlsx
+++ b/Result/checksun_type/工業自動化.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1643,62 +1643,62 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>111.47</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>99.63</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>82.45999999999999</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>99.63</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>82.46</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
@@ -2625,62 +2629,62 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>106.87</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>97.72</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>81.20999999999999</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>97.72</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>81.21</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
@@ -3607,62 +3615,62 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>102.07</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>95.61</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>79.90000000000001</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>95.61</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -3977,7 +3989,7 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
@@ -4589,62 +4601,62 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>97.42999999999999</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>93.58</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>78.54000000000001</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>93.58</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>78.54</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -4959,7 +4975,7 @@
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
@@ -5581,52 +5597,52 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>93.44</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>91.66</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>77.33</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>91.66</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>77.33</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -5941,7 +5961,7 @@
       </c>
       <c r="DQ6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR6" t="inlineStr">
@@ -6558,12 +6578,12 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
@@ -6573,42 +6593,42 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>90.82</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>76.48999999999999</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>90.16</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>76.49</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -6923,7 +6947,7 @@
       </c>
       <c r="DQ7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR7" t="inlineStr">
@@ -7540,57 +7564,57 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>89.25</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>75.87</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>75.87</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -7905,7 +7933,7 @@
       </c>
       <c r="DQ8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR8" t="inlineStr">
@@ -8517,34 +8545,34 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW9" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>87.3</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>75.18000000000001</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>87.1</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>75.18</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9514,7 +9546,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -9524,37 +9556,37 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>86.75999999999999</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>86</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>74.8</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10486,32 +10522,32 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -10521,22 +10557,22 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>1852.0</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>1792.5</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1761.4</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>1792.5</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>1761.4</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11468,57 +11508,57 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>1834.5</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>1784.75</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1761.3</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>1784.75</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>1761.3</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12445,62 +12489,62 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>1811.0</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>1782.75</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1759.9</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>1782.75</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>1759.9</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13427,62 +13475,62 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>1784.0</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>1780.25</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>1756.2</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>1780.25</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>1756.2</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14419,52 +14471,52 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>1762.5</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>1780</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1754.3</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>1780.0</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>1754.3</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15396,57 +15452,57 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>1739.0</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>1773</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1754.2</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>1773.0</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>1754.2</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16378,17 +16438,17 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -16398,37 +16458,37 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>1728.5</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>1765.5</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>1754</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>1765.5</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>1754.0</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17355,62 +17419,62 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>1719.0</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>1756</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>1753.1</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>1756.0</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>1753.1</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,37 +18430,37 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>1716.5</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>1749</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1753.4</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>1749.0</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>1753.4</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>

--- a/Result/checksun_type/工業自動化.xlsx
+++ b/Result/checksun_type/工業自動化.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>487.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1238,562 +1238,562 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>75.33333333333333</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>C1 循環・高峰</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>虧轉盈</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>高峰</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>-82878.0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>12.77</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>10.31</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>-2.10</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>-11.46</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>18.48</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>13.36</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>118.25</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>99.81</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>-0.01412429378531077</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-0.01627486437613013</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>-0.00963149078726977</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>-89.51</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>123554.4959016394</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>86854.0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>99608.6</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>108805.9</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>206835.2</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>151728.18</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>-14071.02838900379</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>21.30</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>倚強科</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>倚強科</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>0.2090924900610291</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>151.1463844797178</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>41.02556967318531</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>72.42</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>31.23</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>39.75</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>自動化設備100.00% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>倚強科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-2.53</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>77.33333333333333</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>C1 循環・高峰</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>虧轉盈</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>高峰</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>88163.0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>78.9</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>10.31</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-1.60</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>-11.06</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>119.4</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>99.18</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>-0.01025163094128612</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-0.01029082774049217</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>-0.004170141784820669</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>-75.03</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>4.52</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>123536.0671232877</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>50802.0</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>96995.0</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>117978.6</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>205262.5</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>150417.52</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>-11017.50347711629</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>倚強科</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>倚強科</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>0.2090924900610291</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>151.1463844797178</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>41.02556967318531</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>4.94</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>32.38</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>72.42</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>31.23</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>40.39</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>自動化設備100.00% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>倚強科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>487.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2010,562 +2010,562 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>104.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>77.33333333333333</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>C1 循環・高峰</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>虧轉盈</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>高峰</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>88163.0</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>10.31</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-1.60</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>-11.06</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>20.39</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>13.14</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>119.4</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>99.18</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-0.01025163094128612</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-0.01029082774049217</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.004170141784820669</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-75.03</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>123554.4959016394</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>50802.0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>96995.0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>117978.6</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>205262.5</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>150417.52</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>-11017.50347711629</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>23.67</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>倚強科</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>倚強科</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>0.2090924900610291</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>151.1463844797178</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>41.02556967318531</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>31.48</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>72.42</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>31.23</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>39.75</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>7501</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>自動化設備100.00% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>倚強科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>其他電子業右上上櫃</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
           <t>107.5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-2.87</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-2.53</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>79.33333333333333</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2026-09-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>C1 循環・高峰</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>虧轉盈</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>高峰</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>12301.0</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>10.29</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>78.9</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>23.53</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>21.67</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>12.94</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>119.9</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>98.55</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-0.006481481481481532</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-0.01149933657673596</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.001252609603340282</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>-65.44</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>123536.0671232877</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>72641.0</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>109559.0</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>136797.8</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>204614.5</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>149919.02</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>-7193.582521251933</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>27.22</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>倚強科</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>倚強科</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>0.2090924900610291</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>151.1463844797178</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>41.02556967318531</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>5.08</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>32.38</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>72.42</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>31.23</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>40.39</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="DI3" t="inlineStr">
-        <is>
-          <t>自動化設備100.00% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>倚強科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>其他電子業右上上櫃</t>
-        </is>
-      </c>
-      <c r="DL3" t="inlineStr">
-        <is>
-          <t>106.5</t>
-        </is>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>108.5</t>
-        </is>
-      </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
@@ -2767,12 +2767,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1147.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>81.33333333333333</t>
+          <t>79.33333333333333</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>194900.0</t>
+          <t>12301.0</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -3087,77 +3087,77 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>119.75</t>
+          <t>119.9</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>98.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.02350813743218805</t>
+          <t>-0.006481481481481532</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-0.02290406222990493</t>
+          <t>-0.01149933657673596</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.002083333333333326</t>
+          <t>0.001252609603340282</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-60.79</t>
+          <t>-65.44</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>118290.0</t>
+          <t>72641.0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>114512.6</t>
+          <t>109559.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>160889.2</t>
+          <t>136797.8</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>204227.3</t>
+          <t>204614.5</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>149099.56</t>
+          <t>149919.02</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-3277.383310652272</t>
+          <t>-7193.582521251933</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -3257,22 +3257,22 @@
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="DL4" t="inlineStr">
         <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>108.5</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
           <t>107.5</t>
-        </is>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>99.7</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>103.5</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1574.0</t>
+          <t>1147.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>83.33333333333333</t>
+          <t>81.33333333333333</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>208515.0</t>
+          <t>194900.0</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>17.23</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -3874,62 +3874,62 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>23.39</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.75</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.02037201062887517</t>
+          <t>-0.02350813743218805</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-0.02073635209479474</t>
+          <t>-0.02290406222990493</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.002841383921109664</t>
+          <t>-0.002083333333333326</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-50.25</t>
+          <t>-60.79</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -3939,37 +3939,37 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>169456.0</t>
+          <t>118290.0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>122826.8</t>
+          <t>114512.6</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>230852.7</t>
+          <t>160889.2</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>204492.5333333333</t>
+          <t>204227.3</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>147208.92</t>
+          <t>149099.56</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>728.3112085476164</t>
+          <t>-3277.383310652272</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -4029,22 +4029,22 @@
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
@@ -4094,22 +4094,22 @@
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>660.0</t>
+          <t>1574.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>85.33333333333333</t>
+          <t>83.33333333333333</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>36574.0</t>
+          <t>208515.0</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -4646,62 +4646,62 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.39</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>119.66</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>96.57</t>
+          <t>97.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.01826086956521733</t>
+          <t>-0.02037201062887517</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-0.02516501650165015</t>
+          <t>-0.02073635209479474</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.008512431521281227</t>
+          <t>0.002841383921109664</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-41.15</t>
+          <t>-50.25</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -4711,37 +4711,37 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>73786.0</t>
+          <t>169456.0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>118003.2</t>
+          <t>122826.8</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>240104.1</t>
+          <t>230852.7</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>201043.2666666667</t>
+          <t>204492.5333333333</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>144256.22</t>
+          <t>147208.92</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>5297.893668263135</t>
+          <t>728.3112085476164</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE6" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI6" t="inlineStr">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1012.0</t>
+          <t>660.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>84.66666666666667</t>
+          <t>85.33333333333333</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>25703.0</t>
+          <t>36574.0</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15.20</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -5433,47 +5433,47 @@
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>118.65</t>
+          <t>119.66</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>96.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.01032702237521521</t>
+          <t>-0.01826086956521733</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-0.01463414634146343</t>
+          <t>-0.02516501650165015</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.01206977438478263</t>
+          <t>0.008512431521281227</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-35.58</t>
+          <t>-41.15</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>113622.0</t>
+          <t>73786.0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>138962.2</t>
+          <t>118003.2</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>253899.9</t>
+          <t>240104.1</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>200398.1666666667</t>
+          <t>201043.2666666667</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>144621.26</t>
+          <t>144256.22</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>11301.69354809288</t>
+          <t>5297.893668263135</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE7" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI7" t="inlineStr">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="DL7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>875.0</t>
+          <t>1012.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>70</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.66666666666667</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>強勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>190282.0</t>
+          <t>25703.0</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>15.20</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -6185,67 +6185,67 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>117.24</t>
+          <t>118.65</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>94.99</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.01608806096528359</t>
+          <t>-0.01032702237521521</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-0.01402805611222446</t>
+          <t>-0.01463414634146343</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.01230463690527595</t>
+          <t>0.01206977438478263</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-28.75</t>
+          <t>-35.58</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -6255,37 +6255,37 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>97409.0</t>
+          <t>113622.0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>164036.6</t>
+          <t>138962.2</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>255871.1</t>
+          <t>253899.9</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>199370.6</t>
+          <t>200398.1666666667</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>142615.86</t>
+          <t>144621.26</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>17215.3500837729</t>
+          <t>11301.69354809288</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE8" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI8" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="DL8" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1375.0</t>
+          <t>875.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -6652,17 +6652,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>82.66666666666667</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6712,174 +6712,174 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>強勢</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>C1 循環・高峰</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>虧轉盈</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>高峰</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>190282.0</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>13.15</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>強勢</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>C1 循環・高峰</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>虧轉盈</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>高峰</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>-23569.0</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="BD9" t="inlineStr">
         <is>
           <t>False</t>
@@ -6947,77 +6947,77 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>8.16</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>11.29</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>115.81</t>
+          <t>117.24</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>94.07</t>
+          <t>94.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.02235099337748347</t>
+          <t>-0.01608806096528359</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-0.01188118811881189</t>
+          <t>-0.01402805611222446</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.01445339873861262</t>
+          <t>0.01230463690527595</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-21.07</t>
+          <t>-28.75</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -7027,37 +7027,37 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>159861.0</t>
+          <t>97409.0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>207265.8</t>
+          <t>164036.6</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>257610.4</t>
+          <t>255871.1</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>199867.7333333333</t>
+          <t>199370.6</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>140923.26</t>
+          <t>142615.86</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>23154.22372786048</t>
+          <t>17215.3500837729</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>37.87</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE9" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI9" t="inlineStr">
@@ -7182,22 +7182,22 @@
       </c>
       <c r="DL9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1245.0</t>
+          <t>1375.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.96</t>
+          <t>-13.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>81.33333333333333</t>
+          <t>82.66666666666667</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>92917.0</t>
+          <t>-23569.0</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7624,17 +7624,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -7719,77 +7719,77 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>487</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>10.70</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>114.16</t>
+          <t>115.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>92.98</t>
+          <t>94.07</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.02106969205834686</t>
+          <t>-0.02235099337748347</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-0.01135473766640571</t>
+          <t>-0.01188118811881189</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.01416959090303371</t>
+          <t>0.01445339873861262</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-16.10</t>
+          <t>-21.07</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -7799,37 +7799,37 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>123536.0671232877</t>
+          <t>123554.4959016394</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>145338.0</t>
+          <t>159861.0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>338878.6</t>
+          <t>207265.8</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>258020.6</t>
+          <t>257610.4</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>198804.3</t>
+          <t>199867.7333333333</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>137844.52</t>
+          <t>140923.26</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>28256.75003102729</t>
+          <t>23154.22372786048</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>37.87</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="DD10" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="DE10" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="DI10" t="inlineStr">
@@ -7954,22 +7954,22 @@
       </c>
       <c r="DL10" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="DS10" t="inlineStr">
         <is>
-          <t>1.704583854574574</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="DT10" t="inlineStr">
@@ -8171,12 +8171,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17552.692</t>
+          <t>23102.211</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1480.0</t>
+          <t>1335.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>48.66666666666666</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -8306,19 +8306,19 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -8381,32 +8381,32 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-3900562.0</t>
+          <t>-11393490.0</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55.80</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -8506,62 +8506,62 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-10.22</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>-14.34</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>1761.0</t>
+          <t>1736.0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1772.7</t>
+          <t>1761.7</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.01592356687898089</t>
+          <t>-0.03754045307443366</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-0.0180815200735519</t>
+          <t>-0.0280898876404494</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.01206171107994392</t>
+          <t>-0.01419647927314027</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-80.78</t>
+          <t>-77.33</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>-81.29</t>
+          <t>-98.84</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-44.96</t>
+          <t>-55.74</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -8571,37 +8571,37 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>25762749995.0</t>
+          <t>30951196515.0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>20302695042.2</t>
+          <t>22782792770.6</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>20319495687.7</t>
+          <t>21686777671.8</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>21709479239.73333</t>
+          <t>21891600841.43333</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>20625102056.66</t>
+          <t>20711483479.08</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>-286035129.6431651</t>
+          <t>-146951378.8972037</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>-21.07</t>
+          <t>-28.80</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
@@ -8661,22 +8661,22 @@
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC11" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="DD11" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE11" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="DG11" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH11" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI11" t="inlineStr">
@@ -8726,27 +8726,27 @@
       </c>
       <c r="DL11" t="inlineStr">
         <is>
-          <t>1525.0</t>
+          <t>1365.0</t>
         </is>
       </c>
       <c r="DM11" t="inlineStr">
         <is>
-          <t>1525.0</t>
+          <t>1395.0</t>
         </is>
       </c>
       <c r="DN11" t="inlineStr">
         <is>
-          <t>1430.0</t>
+          <t>1335.0</t>
         </is>
       </c>
       <c r="DO11" t="inlineStr">
         <is>
-          <t>1480.0</t>
+          <t>1335.0</t>
         </is>
       </c>
       <c r="DP11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ11" t="inlineStr">
@@ -8923,7 +8923,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7474.962</t>
+          <t>17661.692</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1550.0</t>
+          <t>1480.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8968,17 +8968,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>-10.86</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>-4.73</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-4.82</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.66666666666666</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -9083,14 +9083,14 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -9153,32 +9153,32 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>-835283.0</t>
+          <t>-3900562.0</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>56.15</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9258,17 +9258,17 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -9278,62 +9278,62 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>1782.5</t>
+          <t>1761.0</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1780.8</t>
+          <t>1772.7</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>-0.01133501259445846</t>
+          <t>-0.01592356687898089</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>-0.02100210021002102</t>
+          <t>-0.0180815200735519</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>-0.009722222222222188</t>
+          <t>-0.01206171107994392</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-80.78</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>-72.46</t>
+          <t>-81.29</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>-35.88</t>
+          <t>-44.96</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -9343,37 +9343,37 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>11522254920.0</t>
+          <t>25922029736.0</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>18249079458.4</t>
+          <t>20334550990.4</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>20478091327.2</t>
+          <t>20335423661.8</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>22008441937.33333</t>
+          <t>21714788564.43333</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>20654388295.98</t>
+          <t>20628287651.48</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>-299890224.7783739</t>
+          <t>-284197286.477781</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>-17.33</t>
+          <t>-21.07</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
@@ -9433,22 +9433,22 @@
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC12" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="DD12" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE12" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="DG12" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH12" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI12" t="inlineStr">
@@ -9493,32 +9493,32 @@
       </c>
       <c r="DK12" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="DL12" t="inlineStr">
         <is>
-          <t>1565.0</t>
+          <t>1525.0</t>
         </is>
       </c>
       <c r="DM12" t="inlineStr">
         <is>
-          <t>1575.0</t>
+          <t>1525.0</t>
         </is>
       </c>
       <c r="DN12" t="inlineStr">
         <is>
-          <t>1515.0</t>
+          <t>1430.0</t>
         </is>
       </c>
       <c r="DO12" t="inlineStr">
         <is>
-          <t>1550.0</t>
+          <t>1480.0</t>
         </is>
       </c>
       <c r="DP12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ12" t="inlineStr">
@@ -9715,12 +9715,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19380.802</t>
+          <t>7474.962</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1510.0</t>
+          <t>1550.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9740,17 +9740,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-16.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9835,17 +9835,17 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -9855,14 +9855,14 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI13" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -9925,32 +9925,32 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>-2660245.0</t>
+          <t>-835283.0</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>61.61</t>
+          <t>23.76</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -10030,82 +10030,82 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1782.5</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>1785.6</t>
+          <t>1780.8</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>-0.01549907005579665</t>
+          <t>-0.01133501259445846</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>-0.02657710280373837</t>
+          <t>-0.02100210021002102</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>-0.01071723000824398</t>
+          <t>-0.009722222222222188</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>-151.59</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>-67.27</t>
+          <t>-72.46</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>-26.74</t>
+          <t>-35.88</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -10115,37 +10115,37 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
         <is>
-          <t>29396642807.0</t>
+          <t>11522254920.0</t>
         </is>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>18480379331.4</t>
+          <t>18249079458.4</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>21594150400.2</t>
+          <t>20478091327.2</t>
         </is>
       </c>
       <c r="CK13" t="inlineStr">
         <is>
-          <t>22127059699.53333</t>
+          <t>22008441937.33333</t>
         </is>
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>20751845868.18</t>
+          <t>20654388295.98</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>-208396794.1855998</t>
+          <t>-299890224.7783739</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>-19.47</t>
+          <t>-17.33</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="CU13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV13" t="inlineStr">
@@ -10205,22 +10205,22 @@
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.65</t>
         </is>
       </c>
       <c r="DB13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC13" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="DD13" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE13" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="DG13" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH13" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI13" t="inlineStr">
@@ -10270,27 +10270,27 @@
       </c>
       <c r="DL13" t="inlineStr">
         <is>
-          <t>1535.0</t>
+          <t>1565.0</t>
         </is>
       </c>
       <c r="DM13" t="inlineStr">
         <is>
-          <t>1570.0</t>
+          <t>1575.0</t>
         </is>
       </c>
       <c r="DN13" t="inlineStr">
         <is>
-          <t>1490.0</t>
+          <t>1515.0</t>
         </is>
       </c>
       <c r="DO13" t="inlineStr">
         <is>
-          <t>1510.0</t>
+          <t>1550.0</t>
         </is>
       </c>
       <c r="DP13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ13" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10133.625</t>
+          <t>19380.802</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1560.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10512,17 +10512,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>51.33333333333334</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>盤整</t>
+          <t>弱勢</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>-3209734.0</t>
+          <t>-2660245.0</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>61.61</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -10822,62 +10822,62 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>1819.5</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>1791.5</t>
+          <t>1785.6</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>-0.008604794099569713</t>
+          <t>-0.01549907005579665</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>-0.02450142450142445</t>
+          <t>-0.02657710280373837</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>-0.008581937065794798</t>
+          <t>-0.01071723000824398</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>-234.80</t>
+          <t>-151.59</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>-55.59</t>
+          <t>-67.27</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>-16.61</t>
+          <t>-26.74</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -10887,37 +10887,37 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>16121839875.0</t>
+          <t>29396642807.0</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>15439332438.0</t>
+          <t>18480379331.4</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>19742569759.5</t>
+          <t>21594150400.2</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
-          <t>21530836158.63334</t>
+          <t>22127059699.53333</t>
         </is>
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>20853991618.64</t>
+          <t>20751845868.18</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>-228798777.8517644</t>
+          <t>-208396794.1855998</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>-16.80</t>
+          <t>-19.47</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="CU14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV14" t="inlineStr">
@@ -10982,17 +10982,17 @@
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="DB14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC14" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="DD14" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE14" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="DG14" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH14" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI14" t="inlineStr">
@@ -11042,27 +11042,27 @@
       </c>
       <c r="DL14" t="inlineStr">
         <is>
-          <t>1640.0</t>
+          <t>1535.0</t>
         </is>
       </c>
       <c r="DM14" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1570.0</t>
         </is>
       </c>
       <c r="DN14" t="inlineStr">
         <is>
-          <t>1560.0</t>
+          <t>1490.0</t>
         </is>
       </c>
       <c r="DO14" t="inlineStr">
         <is>
-          <t>1560.0</t>
+          <t>1510.0</t>
         </is>
       </c>
       <c r="DP14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ14" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11497.703</t>
+          <t>10133.625</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1625.0</t>
+          <t>1560.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11284,17 +11284,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.8</t>
+          <t>-16.85</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>53.33333333333334</t>
+          <t>51.33333333333334</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -11339,12 +11339,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -11399,14 +11399,14 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -11469,32 +11469,32 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>-2335966.0</t>
+          <t>-3209734.0</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -11574,27 +11574,27 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -11604,52 +11604,52 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>1835.25</t>
+          <t>1819.5</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>1796.6</t>
+          <t>1791.5</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>-0.01928872814948768</t>
+          <t>-0.008604794099569713</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>-0.02364394993045893</t>
+          <t>-0.02450142450142445</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>-0.002987912535651227</t>
+          <t>-0.008581937065794798</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>-555.80</t>
+          <t>-234.80</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-55.59</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-16.61</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -11659,37 +11659,37 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
         <is>
-          <t>18709987614.0</t>
+          <t>16121839875.0</t>
         </is>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>20590762573.0</t>
+          <t>15439332438.0</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>20299103434.5</t>
+          <t>19742569759.5</t>
         </is>
       </c>
       <c r="CK15" t="inlineStr">
         <is>
-          <t>21460328511.46667</t>
+          <t>21530836158.63334</t>
         </is>
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>20899273499.24</t>
+          <t>20853991618.64</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>-88947554.54618636</t>
+          <t>-228798777.8517644</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-16.80</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="CU15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV15" t="inlineStr">
@@ -11749,22 +11749,22 @@
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="DA15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="DB15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC15" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="DD15" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE15" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="DG15" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH15" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI15" t="inlineStr">
@@ -11814,27 +11814,27 @@
       </c>
       <c r="DL15" t="inlineStr">
         <is>
-          <t>1625.0</t>
+          <t>1640.0</t>
         </is>
       </c>
       <c r="DM15" t="inlineStr">
         <is>
-          <t>1660.0</t>
+          <t>1650.0</t>
         </is>
       </c>
       <c r="DN15" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1560.0</t>
         </is>
       </c>
       <c r="DO15" t="inlineStr">
         <is>
-          <t>1625.0</t>
+          <t>1560.0</t>
         </is>
       </c>
       <c r="DP15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ15" t="inlineStr">
@@ -12031,12 +12031,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9564.249</t>
+          <t>11497.703</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1605.0</t>
+          <t>1625.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -12056,17 +12056,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-21.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>55.33333333333334</t>
+          <t>53.33333333333334</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -12171,14 +12171,14 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -12241,32 +12241,32 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>-3274666.0</t>
+          <t>-2335966.0</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -12346,82 +12346,82 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-9.87</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>1840.75</t>
+          <t>1835.25</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>1797.1</t>
+          <t>1796.6</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>-0.02008269344359126</t>
+          <t>-0.01928872814948768</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>-0.0217687074829932</t>
+          <t>-0.02364394993045893</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>-0.002168315489903816</t>
+          <t>-0.002987912535651227</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>-1499.49</t>
+          <t>-555.80</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>-37.38</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -12431,37 +12431,37 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
         <is>
-          <t>15494672076.0</t>
+          <t>18709987614.0</t>
         </is>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>20336296333.2</t>
+          <t>20590762573.0</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>21499317129.8</t>
+          <t>20299103434.5</t>
         </is>
       </c>
       <c r="CK16" t="inlineStr">
         <is>
-          <t>21393574144.16667</t>
+          <t>21460328511.46667</t>
         </is>
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>20871410342.26</t>
+          <t>20899273499.24</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>45483083.24610375</t>
+          <t>-88947554.54618636</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="CU16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV16" t="inlineStr">
@@ -12521,22 +12521,22 @@
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="DB16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC16" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="DD16" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE16" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="DG16" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH16" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI16" t="inlineStr">
@@ -12586,27 +12586,27 @@
       </c>
       <c r="DL16" t="inlineStr">
         <is>
-          <t>1635.0</t>
+          <t>1625.0</t>
         </is>
       </c>
       <c r="DM16" t="inlineStr">
         <is>
-          <t>1645.0</t>
+          <t>1660.0</t>
         </is>
       </c>
       <c r="DN16" t="inlineStr">
         <is>
-          <t>1595.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="DO16" t="inlineStr">
         <is>
-          <t>1605.0</t>
+          <t>1625.0</t>
         </is>
       </c>
       <c r="DP16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ16" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7775.191</t>
+          <t>9564.249</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1640.0</t>
+          <t>1605.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -12828,17 +12828,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-20.22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>57.33333333333334</t>
+          <t>55.33333333333334</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -12943,14 +12943,14 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
           <t>盤整</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="AI17" t="inlineStr">
         <is>
           <t>81.2</t>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>-781070.0</t>
+          <t>-3274666.0</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -13118,17 +13118,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -13138,62 +13138,62 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>1844.75</t>
+          <t>1840.75</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>1798.6</t>
+          <t>1797.1</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>-0.02979942693409743</t>
+          <t>-0.02008269344359126</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>-0.01315789473684215</t>
+          <t>-0.0217687074829932</t>
         </is>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>-0.001893683213850972</t>
+          <t>-0.002168315489903816</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>-297.98</t>
+          <t>-1499.49</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>-25.11</t>
+          <t>-37.38</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -13203,37 +13203,37 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
         <is>
-          <t>12678754285.0</t>
+          <t>15494672076.0</t>
         </is>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>22707103196.0</t>
+          <t>20336296333.2</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>23482165656.2</t>
+          <t>21499317129.8</t>
         </is>
       </c>
       <c r="CK17" t="inlineStr">
         <is>
-          <t>21487294084.3</t>
+          <t>21393574144.16667</t>
         </is>
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>20925535266.54</t>
+          <t>20871410342.26</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>205326755.2438078</t>
+          <t>45483083.24610375</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-14.40</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="CU17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV17" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="CZ17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="DA17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="DB17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC17" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="DD17" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE17" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="DG17" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH17" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI17" t="inlineStr">
@@ -13358,27 +13358,27 @@
       </c>
       <c r="DL17" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1635.0</t>
         </is>
       </c>
       <c r="DM17" t="inlineStr">
         <is>
-          <t>1655.0</t>
+          <t>1645.0</t>
         </is>
       </c>
       <c r="DN17" t="inlineStr">
         <is>
-          <t>1590.0</t>
+          <t>1595.0</t>
         </is>
       </c>
       <c r="DO17" t="inlineStr">
         <is>
-          <t>1640.0</t>
+          <t>1605.0</t>
         </is>
       </c>
       <c r="DP17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ17" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8631.796</t>
+          <t>7775.191</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1635.0</t>
+          <t>1640.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -13600,17 +13600,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-22.85</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>58.66666666666666</t>
+          <t>57.33333333333334</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>-2181570.0</t>
+          <t>-781070.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>-7.9</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00:00</t>
+          <t>2026-10-30 00:00:00</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.44</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -13890,82 +13890,82 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>2,452</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>-6.30</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>1848.25</t>
+          <t>1844.75</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>1798.8</t>
+          <t>1798.6</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>-0.03644395361678632</t>
+          <t>-0.02979942693409743</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>-0.01429327686606674</t>
+          <t>-0.01315789473684215</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>-0.0009459459459459918</t>
+          <t>-0.001893683213850972</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>-157.15</t>
+          <t>-297.98</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -13975,37 +13975,37 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>24033800587.88219</t>
+          <t>24095636417.92623</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
         <is>
-          <t>14191408340.0</t>
+          <t>12678754285.0</t>
         </is>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>24707921469.0</t>
+          <t>22707103196.0</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>23360773648.7</t>
+          <t>23482165656.2</t>
         </is>
       </c>
       <c r="CK18" t="inlineStr">
         <is>
-          <t>22003787059.96667</t>
+          <t>21487294084.3</t>
         </is>
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>21232642194.64</t>
+          <t>20925535266.54</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>327570824.0122527</t>
+          <t>205326755.2438078</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>-12.80</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="CU18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CV18" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="DA18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="DB18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="DC18" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="DD18" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="DE18" t="inlineStr">
@@ -14105,12 +14105,12 @@
       </c>
       <c r="DG18" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>48.27</t>
         </is>
       </c>
       <c r="DH18" t="inlineStr">
         <is>
-          <t>4026192</t>
+          <t>3844364</t>
         </is>
       </c>
       <c r="DI18" t="inlineStr">
@@ -14130,27 +14130,27 @@
       </c>
       <c r="DL18" t="inlineStr">
         <is>
-          <t>1650.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="DM18" t="inlineStr">
         <is>
-          <t>1665.0</t>
+          <t>1655.0</t>
         </is>
       </c>
       <c r="DN18" t="inlineStr">
         <is>
-          <t>1630.0</t>
+          <t>1590.0</t>
         </is>
       </c>
       <c r="DO18" t="inlineStr">
         <is>
-          <t>1635.0</t>
+          <t>1640.0</t>
         </is>
       </c>
       <c r="DP18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ18" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="DS18" t="inlineStr">
         <is>
-          <t>1.122894045541515</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="DT18" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-9.17</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25335.685</t>
+          <t>8631.796</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -14362,567 +14362,567 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>1635.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-22.47</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-4.73</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>58.66666666666666</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>A1 成長型存股</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>-2181570.0</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>-7.9</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2026-10-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>27.44</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>1195.0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>1900.0</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>2,452</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>17662</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>-6.30</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>-5.59</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>1848.25</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>1798.8</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>-0.03644395361678632</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>-0.01429327686606674</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>-0.0009459459459459918</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>-157.15</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>-12.65</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>22.13</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>24095636417.92623</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>14191408340.0</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>24707921469.0</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>23360773648.7</t>
+        </is>
+      </c>
+      <c r="CK19" t="inlineStr">
+        <is>
+          <t>22003787059.96667</t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t>21232642194.64</t>
+        </is>
+      </c>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>327570824.0122527</t>
+        </is>
+      </c>
+      <c r="CN19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CO19" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>-12.80</t>
+        </is>
+      </c>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="CU19" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="CV19" t="inlineStr">
+        <is>
+          <t>1.259581616457139</t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>14.61385886043165</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t>37.22498456914315</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CZ19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="DA19" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="DB19" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="DC19" t="inlineStr">
+        <is>
+          <t>75.86</t>
+        </is>
+      </c>
+      <c r="DD19" t="inlineStr">
+        <is>
+          <t>44.44</t>
+        </is>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>34.08</t>
+        </is>
+      </c>
+      <c r="DF19" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="DG19" t="inlineStr">
+        <is>
+          <t>48.27</t>
+        </is>
+      </c>
+      <c r="DH19" t="inlineStr">
+        <is>
+          <t>3844364</t>
+        </is>
+      </c>
+      <c r="DI19" t="inlineStr">
+        <is>
+          <t>電源及零組件50.00%、基礎設施33.00%、自動化業務10.00%、交通業7.00% (2025年)</t>
+        </is>
+      </c>
+      <c r="DJ19" t="inlineStr">
+        <is>
+          <t>台達電-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="DK19" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="DL19" t="inlineStr">
+        <is>
+          <t>1650.0</t>
+        </is>
+      </c>
+      <c r="DM19" t="inlineStr">
+        <is>
+          <t>1665.0</t>
+        </is>
+      </c>
+      <c r="DN19" t="inlineStr">
+        <is>
           <t>1630.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-10.14</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>-4.82</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>A1 成長型存股</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>-10343950.0</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>2026-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>80.54</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>1195.0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>1900.0</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>7475</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>-9.99</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>-2.11</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>1850.0</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>1798.5</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>-0.03823685608072225</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>-0.0135770234986945</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>0.0002703433360367047</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>-87.19</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>30.83</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>2026/09/21</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>24033800587.88219</t>
-        </is>
-      </c>
-      <c r="CH19" t="inlineStr">
-        <is>
-          <t>41878990550.0</t>
-        </is>
-      </c>
-      <c r="CI19" t="inlineStr">
-        <is>
-          <t>24045807081.0</t>
-        </is>
-      </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t>23100323332.7</t>
-        </is>
-      </c>
-      <c r="CK19" t="inlineStr">
-        <is>
-          <t>22051502506.8</t>
-        </is>
-      </c>
-      <c r="CL19" t="inlineStr">
-        <is>
-          <t>21620258191.54</t>
-        </is>
-      </c>
-      <c r="CM19" t="inlineStr">
-        <is>
-          <t>318921420.9572468</t>
-        </is>
-      </c>
-      <c r="CN19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CO19" t="inlineStr">
-        <is>
-          <t>2026/09/21</t>
-        </is>
-      </c>
-      <c r="CP19" t="inlineStr">
-        <is>
-          <t>-13.07</t>
-        </is>
-      </c>
-      <c r="CQ19" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="CU19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="CV19" t="inlineStr">
-        <is>
-          <t>1.259581616457139</t>
-        </is>
-      </c>
-      <c r="CW19" t="inlineStr">
-        <is>
-          <t>14.61385886043165</t>
-        </is>
-      </c>
-      <c r="CX19" t="inlineStr">
-        <is>
-          <t>37.22498456914315</t>
-        </is>
-      </c>
-      <c r="CY19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CZ19" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="DA19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DB19" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="DC19" t="inlineStr">
-        <is>
-          <t>75.86</t>
-        </is>
-      </c>
-      <c r="DD19" t="inlineStr">
-        <is>
-          <t>49.33</t>
-        </is>
-      </c>
-      <c r="DE19" t="inlineStr">
-        <is>
-          <t>34.08</t>
-        </is>
-      </c>
-      <c r="DF19" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="DG19" t="inlineStr">
-        <is>
-          <t>49.76</t>
-        </is>
-      </c>
-      <c r="DH19" t="inlineStr">
-        <is>
-          <t>4026192</t>
-        </is>
-      </c>
-      <c r="DI19" t="inlineStr">
-        <is>
-          <t>電源及零組件50.00%、基礎設施33.00%、自動化業務10.00%、交通業7.00% (2025年)</t>
-        </is>
-      </c>
-      <c r="DJ19" t="inlineStr">
-        <is>
-          <t>台達電-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="DK19" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="DL19" t="inlineStr">
-        <is>
-          <t>1690.0</t>
-        </is>
-      </c>
-      <c r="DM19" t="inlineStr">
-        <is>
-          <t>1700.0</t>
-        </is>
-      </c>
-      <c r="DN19" t="inlineStr">
-        <is>
-          <t>1610.0</t>
-        </is>
-      </c>
       <c r="DO19" t="inlineStr">
         <is>
-          <t>1630.0</t>
+          <t>1635.0</t>
         </is>
       </c>
       <c r="DP19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="DQ19" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="DS19" t="inlineStr">
         <is>
-          <t>1.090438489331283</t>
+          <t>1.122894045541515</t>
         </is>
       </c>
       <c r="DT19" t="inlineStr">
